--- a/counselor_forms/036_future_husband_application_form--counselor_forms.xlsx
+++ b/counselor_forms/036_future_husband_application_form--counselor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'pizza'}</t>
+          <t>pizza</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Pizza'}</t>
+          <t>Pizza</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tacos'}</t>
+          <t>tacos</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tacos'}</t>
+          <t>Tacos</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sushi'}</t>
+          <t>sushi</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sushi'}</t>
+          <t>Sushi</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'reading'}</t>
+          <t>reading</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Reading'}</t>
+          <t>Reading</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'hiking'}</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Hiking'}</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'playing_video_games'}</t>
+          <t>playing_video_games</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Playing Video Games'}</t>
+          <t>Playing Video Games</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'classical'}</t>
+          <t>classical</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Classical'}</t>
+          <t>Classical</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'hip-hop'}</t>
+          <t>hip-hop</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Hip-Hop'}</t>
+          <t>Hip-Hop</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'electronic'}</t>
+          <t>electronic</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Electronic'}</t>
+          <t>Electronic</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'software_engineer'}</t>
+          <t>software_engineer</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Software Engineer'}</t>
+          <t>Software Engineer</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'lawyer'}</t>
+          <t>lawyer</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Lawyer'}</t>
+          <t>Lawyer</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'the_shawshank_redemption'}</t>
+          <t>the_shawshank_redemption</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'The Shawshank Redemption'}</t>
+          <t>The Shawshank Redemption</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'the_godfather'}</t>
+          <t>the_godfather</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'The Godfather'}</t>
+          <t>The Godfather</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'the_dark_knight'}</t>
+          <t>the_dark_knight</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'The Dark Knight'}</t>
+          <t>The Dark Knight</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'the_great_gatsby'}</t>
+          <t>the_great_gatsby</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'The Great Gatsby'}</t>
+          <t>The Great Gatsby</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'the_catcher_in_the_rye'}</t>
+          <t>the_catcher_in_the_rye</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'The Catcher in the Rye'}</t>
+          <t>The Catcher in the Rye</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'the_little'}</t>
+          <t>the_little</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'The Little'}</t>
+          <t>The Little</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'the_rolling_stones'}</t>
+          <t>the_rolling_stones</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'The Rolling Stones'}</t>
+          <t>The Rolling Stones</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'the_beatles'}</t>
+          <t>the_beatles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'The Beatles'}</t>
+          <t>The Beatles</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'the'}</t>
+          <t>the</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'The'}</t>
+          <t>The</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'mick'}</t>
+          <t>mick</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Mick'}</t>
+          <t>Mick</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'paul'}</t>
+          <t>paul</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Paul'}</t>
+          <t>Paul</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'keith'}</t>
+          <t>keith</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Keith'}</t>
+          <t>Keith</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'football'}</t>
+          <t>football</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Football'}</t>
+          <t>Football</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'basketball'}</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Basketball'}</t>
+          <t>Basketball</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'tennis'}</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Tennis'}</t>
+          <t>Tennis</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'paris'}</t>
+          <t>paris</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Paris'}</t>
+          <t>Paris</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'tokyo'}</t>
+          <t>tokyo</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Tokyo'}</t>
+          <t>Tokyo</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'rio'}</t>
+          <t>rio</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Rio'}</t>
+          <t>Rio</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'hiking'}</t>
+          <t>hiking</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Hiking'}</t>
+          <t>Hiking</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'snorkeling'}</t>
+          <t>snorkeling</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Snorkeling'}</t>
+          <t>Snorkeling</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'sky_diving'}</t>
+          <t>sky_diving</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Sky Diving'}</t>
+          <t>Sky Diving</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'beer'}</t>
+          <t>beer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Beer'}</t>
+          <t>Beer</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'wine'}</t>
+          <t>wine</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Wine'}</t>
+          <t>Wine</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'coffee'}</t>
+          <t>coffee</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Coffee'}</t>
+          <t>Coffee</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'smoker'}</t>
+          <t>smoker</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Smoker'}</t>
+          <t>Smoker</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'non-smoker'}</t>
+          <t>non-smoker</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Non-Smoker'}</t>
+          <t>Non-Smoker</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'ex-smoker'}</t>
+          <t>ex-smoker</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Ex-Smoker'}</t>
+          <t>Ex-Smoker</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'somewhat_active'}</t>
+          <t>somewhat_active</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Somewhat Active'}</t>
+          <t>Somewhat Active</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'very_inactive'}</t>
+          <t>very_inactive</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Very Inactive'}</t>
+          <t>Very Inactive</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
